--- a/samples/survey_rescue13.xlsx
+++ b/samples/survey_rescue13.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H31"/>
+  <dimension ref="A1:AA25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,27 +441,122 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>[구조장비 운용 - 홍아름 강사] 강의 전반에 대해 얼마나 만족하십니까?</t>
+          <t>구조장비 운용 | 홍아름 강사 | 태도: 교수님은 성실한 자세로 노력하며 강의(훈련)하였나요?</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>[붕괴사고 대응 - 홍아름 강사] 강의 전반에 대해 얼마나 만족하십니까?</t>
+          <t>구조장비 운용 | 홍아름 강사 | 준비성: 훈련환경은 적절하고 장비는 충분했나요?</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>[수난구조 이론 - 홍아름 강사] 강의 전반에 대해 얼마나 만족하십니까?</t>
+          <t>구조장비 운용 | 홍아름 강사 | 전문성: 교수님은 전문적이고 숙달된 자세로 훈련을 지도했나요?</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>이번 과정에서 좋았던 점을 자유롭게 적어 주세요.</t>
+          <t>구조장비 운용 | 홍아름 강사 | 적용성: 재난현장 및 실무에서 활용할 수 있는 훈련인가요?</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>개선이 필요한 점을 자유롭게 적어 주세요.</t>
+          <t>구조장비 운용 | 홍아름 강사 | 의견: 이 교과목 또는 강사에 대한 의견을 자유롭게 적어 주세요(선택)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>붕괴사고 대응 | 박로운 강사 | 태도: 강사는 성실하고 열의 있는 자세로 강의하였습니까?</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>붕괴사고 대응 | 박로운 강사 | 목표: 강의 내용은 교과목의 학습목표에 맞게 구성되었습니까?</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>붕괴사고 대응 | 박로운 강사 | 전달: 강사는 강의 내용을 이해하기 쉽게 전달하였습니까?</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>붕괴사고 대응 | 박로운 강사 | 효과: 강의 내용은 현장 직무 수행에 도움이 되겠습니까?</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>붕괴사고 대응 | 박로운 강사 | 의견: 이 교과목 또는 강사에 대한 의견을 자유롭게 적어 주세요(선택)</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>수난구조 이론 | 오여름 강사 | 태도: 강사는 성실하고 열의 있는 자세로 강의하였습니까?</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>수난구조 이론 | 오여름 강사 | 목표: 강의 내용은 교과목의 학습목표에 맞게 구성되었습니까?</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>수난구조 이론 | 오여름 강사 | 전달: 강사는 강의 내용을 이해하기 쉽게 전달하였습니까?</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>수난구조 이론 | 오여름 강사 | 효과: 강의 내용은 현장 직무 수행에 도움이 되겠습니까?</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>수난구조 이론 | 오여름 강사 | 의견: 이 교과목 또는 강사에 대한 의견을 자유롭게 적어 주세요(선택)</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>공통 | 교육시설환경 | 교재의 품질</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>공통 | 교육시설환경 | 강의실 및 교육기자재</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>공통 | 교육시설환경 | 편의시설</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>공통 | 교육시설환경 | 교직원의 친절도</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>공통 | 구내식당 | 구내식당 이용</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>공통 | 구내식당 | 음식의 간</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>공통 | 구내식당 | 메뉴의 다양성</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>공통 | 구내식당 | 청결도</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>공통 | 구내식당 | 친절도</t>
         </is>
       </c>
     </row>
@@ -473,37 +568,116 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>□□소방서</t>
+          <t>△△소방서</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>소방장</t>
+          <t>소방위</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>붕괴사고 대응 강의: 강사님이 열정적으로 진행해 주셨음</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>수난구조 이론 강의: 교구가 부족해 기다리는 시간이 길었음</t>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr"/>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>만족</t>
         </is>
       </c>
     </row>
@@ -515,17 +689,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>○○소방서</t>
+          <t>△△소방서</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>소방장</t>
+          <t>소방사</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -540,12 +714,99 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>구조장비 운용 강의: 질문에 성실하게 답변해 주셔서 좋았음</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>숙소 와이파이가 자주 끊김</t>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>핵심만 짚어 주어 집중이 잘 됐음</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>불만족</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
         </is>
       </c>
     </row>
@@ -562,7 +823,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>소방장</t>
+          <t>소방위</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -577,15 +838,106 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>구조장비 운용 강의: 자료가 깔끔하게 정리되어 복습하기 좋았음</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>질문에 성실하게 답변해 주셔서 좋았음</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -600,26 +952,117 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>소방교</t>
+          <t>소방위</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>만족</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>실습 시간이 부족했음</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr"/>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -629,37 +1072,124 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>○○소방서</t>
+          <t>□□소방서</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>소방위</t>
+          <t>소방사</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>수난구조 이론 강의: 강사님이 열정적으로 진행해 주셨음</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>붕괴사고 대응 강의: 사례가 조금 더 있으면 좋겠음</t>
+          <t>강의실이 더워서 집중하기 어려웠음</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>불만족</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>만족</t>
         </is>
       </c>
     </row>
@@ -671,17 +1201,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>△△소방서</t>
+          <t>소방본부</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>소방위</t>
+          <t>소방교</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -691,11 +1221,102 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>만족</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr"/>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
       <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -705,12 +1326,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>□□소방서</t>
+          <t>소방본부</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>소방위</t>
+          <t>소방장</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -730,10 +1351,97 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>교육 운영 안내가 미리 와서 준비하기 좋았음</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -743,12 +1451,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>□□소방서</t>
+          <t>소방본부</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>소방교</t>
+          <t>소방사</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -758,7 +1466,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -768,10 +1476,97 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>구조장비 운용 강의: 자료가 깔끔하게 정리되어 복습하기 좋았음</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr"/>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>마이크 소리가 작아 뒷자리에서 잘 안 들렸음</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr"/>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -781,17 +1576,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>소방본부</t>
+          <t>□□소방서</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>소방장</t>
+          <t>소방사</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -806,10 +1601,101 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>붕괴사고 대응 강의: 강사님이 열정적으로 진행해 주셨음</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>강의실이 더워서 집중하기 어려웠음</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -819,12 +1705,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>△△소방서</t>
+          <t>소방본부</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>소방위</t>
+          <t>소방사</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -834,7 +1720,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -844,12 +1730,107 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>구조장비 운용 강의: 핵심만 짚어 주어 집중이 잘 됐음</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>붕괴사고 대응 강의: 사례가 조금 더 있으면 좋겠음</t>
+          <t>자료가 깔끔하게 정리되어 복습하기 좋았음</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>자료가 깔끔하게 정리되어 복습하기 좋았음</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>실습 장비가 충분해서 직접 해 볼 수 있었음</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>만족</t>
         </is>
       </c>
     </row>
@@ -866,7 +1847,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>소방사</t>
+          <t>소방교</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -876,22 +1857,105 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>구조장비 운용 강의: 실습 순서를 단계별로 알려 주어 따라가기 쉬웠음</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>강의실이 더워서 집중하기 어려웠음</t>
+          <t>실습 장비가 충분해서 직접 해 볼 수 있었음</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
         </is>
       </c>
     </row>
@@ -903,7 +1967,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>○○소방서</t>
+          <t>소방본부</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -913,7 +1977,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -923,13 +1987,96 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>만족</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>붕괴사고 대응 강의: 자료 글씨가 작아 화면이 잘 안 보였음</t>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>불만족</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr"/>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>만족</t>
         </is>
       </c>
     </row>
@@ -941,12 +2088,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>△△소방서</t>
+          <t>□□소방서</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>소방사</t>
+          <t>소방장</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -956,7 +2103,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -964,8 +2111,107 @@
           <t>매우 만족</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
       <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>마이크 소리가 작아 뒷자리에서 잘 안 들렸음</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>사례가 조금 더 있으면 좋겠음</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -975,17 +2221,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>△△소방서</t>
+          <t>소방본부</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>소방사</t>
+          <t>소방장</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1000,12 +2246,95 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>붕괴사고 대응 강의: 질문에 성실하게 답변해 주셔서 좋았음</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>강의실이 더워서 집중하기 어려웠음</t>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>만족</t>
         </is>
       </c>
     </row>
@@ -1017,22 +2346,22 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>□□소방서</t>
+          <t>△△소방서</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>소방위</t>
+          <t>소방사</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1040,8 +2369,103 @@
           <t>매우 만족</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
       <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>질문에 성실하게 답변해 주셔서 좋았음</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>불만족</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1051,7 +2475,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>△△소방서</t>
+          <t>○○소방서</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1066,22 +2490,109 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>붕괴사고 대응 강의: 핵심만 짚어 주어 집중이 잘 됐음</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>수난구조 이론 강의: 사례가 조금 더 있으면 좋겠음</t>
+          <t>현장 사례를 들어 설명해 이해가 쉬웠음</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>만족</t>
         </is>
       </c>
     </row>
@@ -1093,17 +2604,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>△△소방서</t>
+          <t>○○소방서</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>소방사</t>
+          <t>소방교</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1113,15 +2624,106 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>붕괴사고 대응 강의: 자료가 깔끔하게 정리되어 복습하기 좋았음</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>질문에 성실하게 답변해 주셔서 좋았음</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>불만족</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1131,12 +2733,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>소방본부</t>
+          <t>○○소방서</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>소방교</t>
+          <t>소방위</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1146,7 +2748,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1156,14 +2758,101 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>수난구조 이론 강의: 질문에 성실하게 답변해 주셔서 좋았음</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>구조장비 운용 강의: 교구가 부족해 기다리는 시간이 길었음</t>
-        </is>
-      </c>
+          <t>실습 장비가 충분해서 직접 해 볼 수 있었음</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>점심 직후 시간이라 집중이 어려웠음, 시간 조정 필요</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr"/>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1178,7 +2867,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>소방교</t>
+          <t>소방장</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1188,20 +2877,111 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>구조장비 운용 강의: 질문에 성실하게 답변해 주셔서 좋았음</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr"/>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>강의실이 더워서 집중하기 어려웠음</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr"/>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1211,17 +2991,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>○○소방서</t>
+          <t>□□소방서</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>소방교</t>
+          <t>소방사</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1234,8 +3014,103 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>강의실 의자가 불편했음</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>자료 글씨가 작아 화면이 잘 안 보였음</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1245,17 +3120,17 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>소방본부</t>
+          <t>□□소방서</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>소방사</t>
+          <t>소방장</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1270,10 +3145,97 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>구조장비 운용 강의: 현장 사례를 들어 설명해 이해가 쉬웠음</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr"/>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>핵심만 짚어 주어 집중이 잘 됐음</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr"/>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr"/>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1283,7 +3245,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>소방본부</t>
+          <t>□□소방서</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1303,13 +3265,100 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>만족</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>붕괴사고 대응 강의: 교구가 부족해 기다리는 시간이 길었음</t>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr"/>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>만족</t>
         </is>
       </c>
     </row>
@@ -1321,7 +3370,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>○○소방서</t>
+          <t>△△소방서</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1341,259 +3390,114 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>교육 운영 안내가 미리 와서 준비하기 좋았음</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>구조장비 운용 강의: 설명 속도가 빨라 따라가기 어려웠음</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>2026/10/30 오후 05:09:00</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>□□소방서</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>소방위</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>구조장비 운용 강의: 핵심만 짚어 주어 집중이 잘 됐음</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>구조장비 운용 강의: 교구가 부족해 기다리는 시간이 길었음</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>2026/10/30 오후 05:12:00</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>소방본부</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>소방교</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>수난구조 이론 강의: 질문에 성실하게 답변해 주셔서 좋았음</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>2026/10/30 오후 05:15:00</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>○○소방서</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>소방교</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>보통</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>보통</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>수난구조 이론 강의: 강사님이 열정적으로 진행해 주셨음</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>2026/10/30 오후 05:18:00</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>△△소방서</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>소방위</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>구조장비 운용 강의: 핵심만 짚어 주어 집중이 잘 됐음</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>강의실이 더워서 집중하기 어려웠음</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>2026/10/30 오후 05:21:00</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>△△소방서</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>소방장</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>구조장비 운용 강의: 실습 장비가 충분해서 직접 해 볼 수 있었음</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>수난구조 이론 강의: 설명 속도가 빨라 따라가기 어려웠음</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>2026/10/30 오후 05:24:00</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>○○소방서</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>소방위</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>보통</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>교육 운영 안내가 미리 와서 준비하기 좋았음</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr"/>
+          <t>자료 글씨가 작아 화면이 잘 안 보였음</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>최신 법령 개정 내용을 알려 주어 실무에 도움이 됨</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>불만족</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>현장 사례를 들어 설명해 이해가 쉬웠음</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/samples/survey_rescue13.xlsx
+++ b/samples/survey_rescue13.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA25"/>
+  <dimension ref="A1:AB26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -559,6 +559,11 @@
           <t>공통 | 구내식당 | 친절도</t>
         </is>
       </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>공통 | 과정 운영 | 의견: 이번 과정 운영(일정·시설·안내 등)에 대한 의견을 자유롭게 적어 주세요(선택)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -573,7 +578,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>소방위</t>
+          <t>소방사</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -583,7 +588,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -604,20 +609,24 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr"/>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>실습 장비가 충분해서 직접 해 볼 수 있었음</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr">
         <is>
           <t>만족</t>
@@ -630,7 +639,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -641,7 +650,7 @@
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -651,12 +660,12 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -666,7 +675,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -674,12 +683,17 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr"/>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>만족</t>
-        </is>
-      </c>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -689,12 +703,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>△△소방서</t>
+          <t>소방본부</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>소방사</t>
+          <t>소방교</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -704,17 +718,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
@@ -725,7 +739,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -735,43 +749,39 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>만족</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>핵심만 짚어 주어 집중이 잘 됐음</t>
-        </is>
-      </c>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>불만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -786,12 +796,12 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -806,9 +816,10 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -818,7 +829,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>○○소방서</t>
+          <t>□□소방서</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -828,32 +839,32 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>질문에 성실하게 답변해 주셔서 좋았음</t>
+          <t>핵심만 짚어 주어 집중이 잘 됐음</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -863,18 +874,18 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -889,23 +900,23 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -920,7 +931,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -930,14 +941,15 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -947,17 +959,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>△△소방서</t>
+          <t>소방본부</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>소방위</t>
+          <t>소방장</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -967,17 +979,17 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>실습 시간이 부족했음</t>
+          <t>설명 속도가 빨라 따라가기 어려웠음</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -997,7 +1009,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="M6" t="inlineStr"/>
@@ -1021,7 +1033,11 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr"/>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>이론 비중이 높아 실무 내용이 더 필요함</t>
+        </is>
+      </c>
       <c r="S6" t="inlineStr">
         <is>
           <t>매우 만족</t>
@@ -1034,12 +1050,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1049,7 +1065,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1057,10 +1073,19 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>교육생 질문에 담당자가 빠르게 답해 주었음</t>
         </is>
       </c>
     </row>
@@ -1072,22 +1097,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>□□소방서</t>
+          <t>○○소방서</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>소방사</t>
+          <t>소방위</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1100,11 +1125,7 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>강의실이 더워서 집중하기 어려웠음</t>
-        </is>
-      </c>
+      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
           <t>만족</t>
@@ -1117,7 +1138,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1128,12 +1149,12 @@
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1143,18 +1164,22 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>강의실 의자가 불편했음</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
           <t>불만족</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr"/>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1164,32 +1189,37 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>만족</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>주차 공간이 부족했음</t>
         </is>
       </c>
     </row>
@@ -1201,17 +1231,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>소방본부</t>
+          <t>△△소방서</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>소방교</t>
+          <t>소방사</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1221,12 +1251,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
@@ -1247,13 +1277,17 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>만족</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr"/>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>최신 법령 개정 내용을 알려 주어 실무에 도움이 됨</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1263,18 +1297,22 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>보통</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr"/>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>자료가 깔끔하게 정리되어 복습하기 좋았음</t>
+        </is>
+      </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
@@ -1289,17 +1327,17 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1314,7 +1352,12 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>강의실이 더워서 집중하기 어려웠음</t>
         </is>
       </c>
     </row>
@@ -1326,17 +1369,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>소방본부</t>
+          <t>○○소방서</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>소방장</t>
+          <t>소방위</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1351,7 +1394,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="H9" t="inlineStr"/>
@@ -1362,17 +1405,17 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="M9" t="inlineStr"/>
@@ -1399,12 +1442,12 @@
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1419,12 +1462,12 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -1432,16 +1475,13 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
+      <c r="Z9" t="inlineStr"/>
       <c r="AA9" t="inlineStr">
         <is>
           <t>만족</t>
         </is>
       </c>
+      <c r="AB9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1456,7 +1496,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>소방사</t>
+          <t>소방장</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1466,22 +1506,22 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>마이크 소리가 작아 뒷자리에서 잘 안 들렸음</t>
+          <t>자료 글씨가 작아 화면이 잘 안 보였음</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1491,17 +1531,17 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="M10" t="inlineStr"/>
@@ -1512,12 +1552,12 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
@@ -1533,17 +1573,17 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
@@ -1553,7 +1593,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
@@ -1561,10 +1601,19 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>교육 운영 안내가 미리 와서 준비하기 좋았음</t>
         </is>
       </c>
     </row>
@@ -1576,22 +1625,22 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>□□소방서</t>
+          <t>○○소방서</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>소방사</t>
+          <t>소방위</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1607,7 +1656,7 @@
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1617,7 +1666,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1627,7 +1676,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>강의실이 더워서 집중하기 어려웠음</t>
+          <t>질문에 성실하게 답변해 주셔서 좋았음</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1642,7 +1691,7 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
@@ -1663,12 +1712,12 @@
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
@@ -1678,7 +1727,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
@@ -1688,14 +1737,15 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1705,12 +1755,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>소방본부</t>
+          <t>○○소방서</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>소방사</t>
+          <t>소방교</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1720,7 +1770,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1735,37 +1785,33 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>자료가 깔끔하게 정리되어 복습하기 좋았음</t>
+          <t>질문에 성실하게 답변해 주셔서 좋았음</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>만족</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>자료가 깔끔하게 정리되어 복습하기 좋았음</t>
-        </is>
-      </c>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -1775,7 +1821,7 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
@@ -1783,34 +1829,30 @@
           <t>보통</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>실습 장비가 충분해서 직접 해 볼 수 있었음</t>
-        </is>
-      </c>
+      <c r="R12" t="inlineStr"/>
       <c r="S12" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -1825,14 +1867,15 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>만족</t>
-        </is>
-      </c>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1842,12 +1885,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>△△소방서</t>
+          <t>○○소방서</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>소방교</t>
+          <t>소방사</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1862,7 +1905,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1870,11 +1913,7 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>실습 장비가 충분해서 직접 해 볼 수 있었음</t>
-        </is>
-      </c>
+      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
           <t>매우 만족</t>
@@ -1882,17 +1921,17 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="M13" t="inlineStr"/>
@@ -1903,61 +1942,62 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>만족</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr"/>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
       <c r="Z13" t="inlineStr">
         <is>
           <t>만족</t>
         </is>
       </c>
-      <c r="AA13" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
+      <c r="AA13" t="inlineStr"/>
+      <c r="AB13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1967,7 +2007,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>소방본부</t>
+          <t>△△소방서</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1977,7 +2017,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -2013,7 +2053,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="M14" t="inlineStr"/>
@@ -2029,7 +2069,7 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
@@ -2037,41 +2077,45 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="R14" t="inlineStr"/>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>강의실이 더워서 집중하기 어려웠음</t>
+        </is>
+      </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>불만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
-      <c r="W14" t="inlineStr"/>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
       <c r="X14" t="inlineStr">
         <is>
           <t>매우 만족</t>
         </is>
       </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+      <c r="Y14" t="inlineStr"/>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2079,6 +2123,7 @@
           <t>만족</t>
         </is>
       </c>
+      <c r="AB14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2088,7 +2133,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>□□소방서</t>
+          <t>○○소방서</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2108,7 +2153,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -2116,20 +2161,24 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr"/>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>질문에 성실하게 답변해 주셔서 좋았음</t>
+        </is>
+      </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -2137,79 +2186,72 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr">
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr"/>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
         <is>
           <t>마이크 소리가 작아 뒷자리에서 잘 안 들렸음</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>보통</t>
-        </is>
-      </c>
-      <c r="R15" t="inlineStr">
-        <is>
-          <t>사례가 조금 더 있으면 좋겠음</t>
-        </is>
-      </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>보통</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>보통</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>만족</t>
         </is>
       </c>
     </row>
@@ -2221,17 +2263,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>소방본부</t>
+          <t>○○소방서</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>소방장</t>
+          <t>소방위</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -2241,12 +2283,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="H16" t="inlineStr"/>
@@ -2267,7 +2309,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="M16" t="inlineStr"/>
@@ -2283,15 +2325,19 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>만족</t>
-        </is>
-      </c>
-      <c r="R16" t="inlineStr"/>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>마이크 소리가 작아 뒷자리에서 잘 안 들렸음</t>
+        </is>
+      </c>
       <c r="S16" t="inlineStr">
         <is>
           <t>만족</t>
@@ -2299,7 +2345,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2314,7 +2360,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -2324,19 +2370,16 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>만족</t>
-        </is>
-      </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr"/>
+      <c r="AB16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2346,22 +2389,22 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>△△소방서</t>
+          <t>□□소방서</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>소방사</t>
+          <t>소방교</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -2371,7 +2414,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="H17" t="inlineStr"/>
@@ -2382,27 +2425,23 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>만족</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>질문에 성실하게 답변해 주셔서 좋았음</t>
-        </is>
-      </c>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -2417,7 +2456,7 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>불만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="R17" t="inlineStr"/>
@@ -2433,12 +2472,12 @@
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
@@ -2451,19 +2490,16 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>보통</t>
-        </is>
-      </c>
+      <c r="Y17" t="inlineStr"/>
       <c r="Z17" t="inlineStr">
         <is>
           <t>만족</t>
         </is>
       </c>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t>보통</t>
+      <c r="AA17" t="inlineStr"/>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>쉬는 시간이 짧아 이동하기 바빴음</t>
         </is>
       </c>
     </row>
@@ -2480,7 +2516,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>소방위</t>
+          <t>소방교</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2490,22 +2526,22 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>현장 사례를 들어 설명해 이해가 쉬웠음</t>
+          <t>핵심만 짚어 주어 집중이 잘 됐음</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2515,12 +2551,12 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -2531,7 +2567,7 @@
       <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
@@ -2541,7 +2577,7 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
@@ -2549,15 +2585,19 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="R18" t="inlineStr"/>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>설명 속도가 빨라 따라가기 어려웠음</t>
+        </is>
+      </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2567,7 +2607,7 @@
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
@@ -2577,22 +2617,27 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>만족</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>쉬는 시간이 짧아 이동하기 바빴음</t>
         </is>
       </c>
     </row>
@@ -2604,12 +2649,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>○○소방서</t>
+          <t>□□소방서</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>소방교</t>
+          <t>소방위</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2624,18 +2669,18 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2650,22 +2695,22 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>질문에 성실하게 답변해 주셔서 좋았음</t>
+          <t>자료 글씨가 작아 화면이 잘 안 보였음</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>불만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2675,55 +2720,52 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="R19" t="inlineStr"/>
       <c r="S19" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>만족</t>
-        </is>
-      </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr"/>
       <c r="X19" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2733,12 +2775,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>○○소방서</t>
+          <t>□□소방서</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>소방위</t>
+          <t>소방사</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2748,12 +2790,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -2761,11 +2803,7 @@
           <t>매우 만족</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>실습 장비가 충분해서 직접 해 볼 수 있었음</t>
-        </is>
-      </c>
+      <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
           <t>매우 만족</t>
@@ -2778,32 +2816,28 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>점심 직후 시간이라 집중이 어려웠음, 시간 조정 필요</t>
-        </is>
-      </c>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>불만족</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
@@ -2819,7 +2853,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -2829,7 +2863,7 @@
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
@@ -2844,15 +2878,20 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr"/>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>강의실 의자가 불편했음</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2862,39 +2901,35 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>□□소방서</t>
+          <t>소방본부</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>소방장</t>
+          <t>소방위</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>강의실이 더워서 집중하기 어려웠음</t>
-        </is>
-      </c>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
           <t>매우 만족</t>
@@ -2902,7 +2937,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -2912,49 +2947,49 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="R21" t="inlineStr"/>
       <c r="S21" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
@@ -2964,7 +2999,7 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
@@ -2974,12 +3009,17 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>교육 운영 안내가 미리 와서 준비하기 좋았음</t>
         </is>
       </c>
     </row>
@@ -3021,33 +3061,33 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>강의실 의자가 불편했음</t>
+          <t>교구가 부족해 기다리는 시간이 길었음</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
@@ -3057,7 +3097,7 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
@@ -3067,7 +3107,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>자료 글씨가 작아 화면이 잘 안 보였음</t>
+          <t>강의실이 더워서 집중하기 어려웠음</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -3077,17 +3117,17 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
@@ -3110,7 +3150,12 @@
           <t>매우 만족</t>
         </is>
       </c>
-      <c r="AA22" t="inlineStr"/>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -3125,7 +3170,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>소방장</t>
+          <t>소방위</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3135,7 +3180,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -3150,12 +3195,12 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>핵심만 짚어 주어 집중이 잘 됐음</t>
+          <t>실습 장비가 충분해서 직접 해 볼 수 있었음</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3176,17 +3221,17 @@
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>불만족</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
@@ -3207,7 +3252,7 @@
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
@@ -3217,13 +3262,17 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>보통</t>
-        </is>
-      </c>
-      <c r="X23" t="inlineStr"/>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
@@ -3233,9 +3282,10 @@
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -3245,7 +3295,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>□□소방서</t>
+          <t>○○소방서</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -3260,12 +3310,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -3276,12 +3326,12 @@
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -3291,7 +3341,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="M24" t="inlineStr"/>
@@ -3302,23 +3352,23 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="R24" t="inlineStr"/>
       <c r="S24" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
@@ -3328,12 +3378,12 @@
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="W24" t="inlineStr">
@@ -3341,26 +3391,23 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+      <c r="X24" t="inlineStr"/>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>만족</t>
-        </is>
-      </c>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -3370,12 +3417,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>△△소방서</t>
+          <t>○○소방서</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>소방교</t>
+          <t>소방장</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3395,14 +3442,10 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>만족</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>자료 글씨가 작아 화면이 잘 안 보였음</t>
-        </is>
-      </c>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
           <t>만족</t>
@@ -3410,22 +3453,22 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>최신 법령 개정 내용을 알려 주어 실무에 도움이 됨</t>
+          <t>강사님이 열정적으로 진행해 주셨음</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -3435,24 +3478,20 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>불만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>보통</t>
-        </is>
-      </c>
-      <c r="R25" t="inlineStr">
-        <is>
-          <t>현장 사례를 들어 설명해 이해가 쉬웠음</t>
-        </is>
-      </c>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr"/>
       <c r="S25" t="inlineStr">
         <is>
           <t>만족</t>
@@ -3465,7 +3504,7 @@
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
@@ -3475,12 +3514,12 @@
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
@@ -3496,6 +3535,145 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026/10/30 오후 05:09:00</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>소방본부</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>소방위</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>실습 순서를 단계별로 알려 주어 따라가기 쉬웠음</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>이론 비중이 높아 실무 내용이 더 필요함</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>과정 전체 일정 구성이 알찼음</t>
         </is>
       </c>
     </row>

--- a/samples/survey_rescue13.xlsx
+++ b/samples/survey_rescue13.xlsx
@@ -441,77 +441,77 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>구조장비 운용 | 홍아름 강사 | 태도: 교수님은 성실한 자세로 노력하며 강의(훈련)하였나요?</t>
+          <t>구조장비 운용 | 박솔빈 강사 | 태도: 교수님은 성실한 자세로 노력하며 강의(훈련)하였나요?</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>구조장비 운용 | 홍아름 강사 | 준비성: 훈련환경은 적절하고 장비는 충분했나요?</t>
+          <t>구조장비 운용 | 박솔빈 강사 | 준비성: 훈련환경은 적절하고 장비는 충분했나요?</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>구조장비 운용 | 홍아름 강사 | 전문성: 교수님은 전문적이고 숙달된 자세로 훈련을 지도했나요?</t>
+          <t>구조장비 운용 | 박솔빈 강사 | 전문성: 교수님은 전문적이고 숙달된 자세로 훈련을 지도했나요?</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>구조장비 운용 | 홍아름 강사 | 적용성: 재난현장 및 실무에서 활용할 수 있는 훈련인가요?</t>
+          <t>구조장비 운용 | 박솔빈 강사 | 적용성: 재난현장 및 실무에서 활용할 수 있는 훈련인가요?</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>구조장비 운용 | 홍아름 강사 | 의견: 이 교과목 또는 강사에 대한 의견을 자유롭게 적어 주세요(선택)</t>
+          <t>구조장비 운용 | 박솔빈 강사 | 의견: 이 교과목 또는 강사에 대한 의견을 자유롭게 적어 주세요(선택)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>붕괴사고 대응 | 박로운 강사 | 태도: 강사는 성실하고 열의 있는 자세로 강의하였습니까?</t>
+          <t>붕괴사고 대응 | 김새봄 강사 | 태도: 강사는 성실하고 열의 있는 자세로 강의하였습니까?</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>붕괴사고 대응 | 박로운 강사 | 목표: 강의 내용은 교과목의 학습목표에 맞게 구성되었습니까?</t>
+          <t>붕괴사고 대응 | 김새봄 강사 | 목표: 강의 내용은 교과목의 학습목표에 맞게 구성되었습니까?</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>붕괴사고 대응 | 박로운 강사 | 전달: 강사는 강의 내용을 이해하기 쉽게 전달하였습니까?</t>
+          <t>붕괴사고 대응 | 김새봄 강사 | 전달: 강사는 강의 내용을 이해하기 쉽게 전달하였습니까?</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>붕괴사고 대응 | 박로운 강사 | 효과: 강의 내용은 현장 직무 수행에 도움이 되겠습니까?</t>
+          <t>붕괴사고 대응 | 김새봄 강사 | 효과: 강의 내용은 현장 직무 수행에 도움이 되겠습니까?</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>붕괴사고 대응 | 박로운 강사 | 의견: 이 교과목 또는 강사에 대한 의견을 자유롭게 적어 주세요(선택)</t>
+          <t>붕괴사고 대응 | 김새봄 강사 | 의견: 이 교과목 또는 강사에 대한 의견을 자유롭게 적어 주세요(선택)</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>수난구조 이론 | 오여름 강사 | 태도: 강사는 성실하고 열의 있는 자세로 강의하였습니까?</t>
+          <t>수난구조 이론 | 김새봄 강사 | 태도: 강사는 성실하고 열의 있는 자세로 강의하였습니까?</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>수난구조 이론 | 오여름 강사 | 목표: 강의 내용은 교과목의 학습목표에 맞게 구성되었습니까?</t>
+          <t>수난구조 이론 | 김새봄 강사 | 목표: 강의 내용은 교과목의 학습목표에 맞게 구성되었습니까?</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>수난구조 이론 | 오여름 강사 | 전달: 강사는 강의 내용을 이해하기 쉽게 전달하였습니까?</t>
+          <t>수난구조 이론 | 김새봄 강사 | 전달: 강사는 강의 내용을 이해하기 쉽게 전달하였습니까?</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>수난구조 이론 | 오여름 강사 | 효과: 강의 내용은 현장 직무 수행에 도움이 되겠습니까?</t>
+          <t>수난구조 이론 | 김새봄 강사 | 효과: 강의 내용은 현장 직무 수행에 도움이 되겠습니까?</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>수난구조 이론 | 오여름 강사 | 의견: 이 교과목 또는 강사에 대한 의견을 자유롭게 적어 주세요(선택)</t>
+          <t>수난구조 이론 | 김새봄 강사 | 의견: 이 교과목 또는 강사에 대한 의견을 자유롭게 적어 주세요(선택)</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -568,27 +568,27 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026/10/30 오후 04:00:00</t>
+          <t>2026/10/28 오후 04:00:00</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>△△소방서</t>
+          <t>□□소방서</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>소방사</t>
+          <t>소방장</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -598,10 +598,14 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>점심 직후 시간이라 집중이 어려웠음, 시간 조정 필요</t>
+        </is>
+      </c>
       <c r="I3" t="inlineStr">
         <is>
           <t>매우 만족</t>
@@ -622,24 +626,20 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>실습 장비가 충분해서 직접 해 볼 수 있었음</t>
-        </is>
-      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -647,7 +647,11 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr"/>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>사례가 조금 더 있으면 좋겠음</t>
+        </is>
+      </c>
       <c r="S3" t="inlineStr">
         <is>
           <t>만족</t>
@@ -665,7 +669,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -675,7 +679,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -685,12 +689,12 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr"/>
@@ -698,27 +702,27 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026/10/30 오후 04:03:00</t>
+          <t>2026/10/28 오후 04:03:00</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>소방본부</t>
+          <t>□□소방서</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>소방교</t>
+          <t>소방장</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -734,59 +738,59 @@
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -796,55 +800,51 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>만족</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr"/>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>만족</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr"/>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr"/>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>주차 공간이 부족했음</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026/10/30 오후 04:06:00</t>
+          <t>2026/10/28 오후 04:06:00</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>□□소방서</t>
+          <t>△△소방서</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>소방위</t>
+          <t>소방사</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -857,11 +857,7 @@
           <t>매우 만족</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>핵심만 짚어 주어 집중이 잘 됐음</t>
-        </is>
-      </c>
+      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
           <t>매우 만족</t>
@@ -911,12 +907,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -926,12 +922,12 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -941,12 +937,12 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr"/>
@@ -954,7 +950,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026/10/30 오후 04:09:00</t>
+          <t>2026/10/28 오후 04:09:00</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -969,7 +965,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -984,14 +980,10 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>설명 속도가 빨라 따라가기 어려웠음</t>
-        </is>
-      </c>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
           <t>매우 만족</t>
@@ -999,17 +991,17 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="M6" t="inlineStr"/>
@@ -1020,27 +1012,23 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>만족</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>이론 비중이 높아 실무 내용이 더 필요함</t>
-        </is>
-      </c>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1050,17 +1038,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1070,7 +1058,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1080,39 +1068,35 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>보통</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>교육생 질문에 담당자가 빠르게 답해 주었음</t>
-        </is>
-      </c>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026/10/30 오후 04:12:00</t>
+          <t>2026/10/28 오후 04:12:00</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>○○소방서</t>
+          <t>소방본부</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>소방위</t>
+          <t>소방사</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1125,7 +1109,11 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>실습 순서를 단계별로 알려 주어 따라가기 쉬웠음</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr">
         <is>
           <t>만족</t>
@@ -1133,7 +1121,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1149,7 +1137,7 @@
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1159,7 +1147,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -1167,19 +1155,15 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>강의실 의자가 불편했음</t>
-        </is>
-      </c>
+      <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr">
         <is>
-          <t>불만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1189,12 +1173,12 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1204,7 +1188,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1217,36 +1201,32 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>주차 공간이 부족했음</t>
-        </is>
-      </c>
+      <c r="AB7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026/10/30 오후 04:15:00</t>
+          <t>2026/10/28 오후 04:15:00</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>△△소방서</t>
+          <t>소방본부</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>소방사</t>
+          <t>소방위</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1256,18 +1236,18 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1280,11 +1260,7 @@
           <t>매우 만족</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>최신 법령 개정 내용을 알려 주어 실무에 도움이 됨</t>
-        </is>
-      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
           <t>만족</t>
@@ -1292,12 +1268,12 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
@@ -1307,7 +1283,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>자료가 깔끔하게 정리되어 복습하기 좋았음</t>
+          <t>핵심만 짚어 주어 집중이 잘 됐음</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1322,49 +1298,45 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>보통</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>강의실이 더워서 집중하기 어려웠음</t>
-        </is>
-      </c>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026/10/30 오후 04:18:00</t>
+          <t>2026/10/28 오후 04:18:00</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1394,7 +1366,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="H9" t="inlineStr"/>
@@ -1418,31 +1390,35 @@
           <t>매우 만족</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>실습 시간이 부족했음</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
@@ -1452,7 +1428,7 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1462,7 +1438,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -1475,7 +1451,11 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>만족</t>
@@ -1486,22 +1466,22 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026/10/30 오후 04:21:00</t>
+          <t>2026/10/28 오후 04:21:00</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>소방본부</t>
+          <t>□□소방서</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>소방장</t>
+          <t>소방위</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1519,11 +1499,7 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>자료 글씨가 작아 화면이 잘 안 보였음</t>
-        </is>
-      </c>
+      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
           <t>매우 만족</t>
@@ -1531,12 +1507,12 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1552,7 +1528,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1562,43 +1538,43 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
@@ -1611,31 +1587,27 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>교육 운영 안내가 미리 와서 준비하기 좋았음</t>
-        </is>
-      </c>
+      <c r="AB10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026/10/30 오후 04:24:00</t>
+          <t>2026/10/28 오후 04:24:00</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>○○소방서</t>
+          <t>소방본부</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>소방위</t>
+          <t>소방장</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1645,7 +1617,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1653,7 +1625,11 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr"/>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>질문에 성실하게 답변해 주셔서 좋았음</t>
+        </is>
+      </c>
       <c r="I11" t="inlineStr">
         <is>
           <t>만족</t>
@@ -1671,14 +1647,10 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>질문에 성실하게 답변해 주셔서 좋았음</t>
-        </is>
-      </c>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
           <t>만족</t>
@@ -1691,7 +1663,7 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
@@ -1699,7 +1671,11 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr"/>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>교구가 부족해 기다리는 시간이 길었음</t>
+        </is>
+      </c>
       <c r="S11" t="inlineStr">
         <is>
           <t>매우 만족</t>
@@ -1707,7 +1683,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1722,12 +1698,12 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
@@ -1737,7 +1713,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1750,57 +1726,53 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026/10/30 오후 04:27:00</t>
+          <t>2026/10/28 오후 04:27:00</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>○○소방서</t>
+          <t>□□소방서</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>소방교</t>
+          <t>소방장</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>질문에 성실하게 답변해 주셔서 좋았음</t>
-        </is>
-      </c>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1811,12 +1783,12 @@
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1826,13 +1798,13 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
@@ -1847,17 +1819,17 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
@@ -1880,17 +1852,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026/10/30 오후 04:30:00</t>
+          <t>2026/10/28 오후 04:30:00</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>○○소방서</t>
+          <t>□□소방서</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>소방사</t>
+          <t>소방위</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1910,18 +1882,18 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1937,17 +1909,17 @@
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
@@ -1963,17 +1935,17 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
@@ -1988,21 +1960,25 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>만족</t>
-        </is>
-      </c>
-      <c r="AA13" t="inlineStr"/>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
       <c r="AB13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026/10/30 오후 04:33:00</t>
+          <t>2026/10/28 오후 04:33:00</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -2012,12 +1988,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>소방교</t>
+          <t>소방사</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -2032,34 +2008,38 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr"/>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>실습 시간이 부족했음</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -2069,76 +2049,76 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>만족</t>
-        </is>
-      </c>
-      <c r="R14" t="inlineStr">
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr"/>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
         <is>
           <t>강의실이 더워서 집중하기 어려웠음</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>보통</t>
-        </is>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr"/>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026/10/30 오후 04:36:00</t>
+          <t>2026/10/28 오후 04:36:00</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>○○소방서</t>
+          <t>소방본부</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>소방장</t>
+          <t>소방교</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2148,22 +2128,22 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>질문에 성실하게 답변해 주셔서 좋았음</t>
+          <t>실습 순서를 단계별로 알려 주어 따라가기 쉬웠음</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2178,7 +2158,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -2189,17 +2169,17 @@
       <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
@@ -2207,7 +2187,11 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="R15" t="inlineStr"/>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>설명 속도가 빨라 따라가기 어려웠음</t>
+        </is>
+      </c>
       <c r="S15" t="inlineStr">
         <is>
           <t>만족</t>
@@ -2225,7 +2209,7 @@
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
@@ -2235,30 +2219,26 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>보통</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr"/>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>보통</t>
-        </is>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>보통</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>마이크 소리가 작아 뒷자리에서 잘 안 들렸음</t>
-        </is>
-      </c>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr"/>
+      <c r="AB15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026/10/30 오후 04:39:00</t>
+          <t>2026/10/28 오후 04:39:00</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2268,7 +2248,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>소방위</t>
+          <t>소방장</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2294,12 +2274,12 @@
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -2312,25 +2292,29 @@
           <t>매우 만족</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>점심 직후 시간이라 집중이 어려웠음, 시간 조정 필요</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
@@ -2345,7 +2329,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2360,7 +2344,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -2368,38 +2352,38 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
+      <c r="Y16" t="inlineStr"/>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>보통</t>
-        </is>
-      </c>
-      <c r="AA16" t="inlineStr"/>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
       <c r="AB16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026/10/30 오후 04:42:00</t>
+          <t>2026/10/28 오후 04:42:00</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>□□소방서</t>
+          <t>소방본부</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>소방교</t>
+          <t>소방장</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -2409,39 +2393,39 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -2451,18 +2435,18 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
@@ -2472,7 +2456,7 @@
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
@@ -2487,71 +2471,71 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>만족</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr"/>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>만족</t>
-        </is>
-      </c>
-      <c r="AA17" t="inlineStr"/>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>쉬는 시간이 짧아 이동하기 바빴음</t>
-        </is>
-      </c>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026/10/30 오후 04:45:00</t>
+          <t>2026/10/28 오후 04:45:00</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>○○소방서</t>
+          <t>소방본부</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>소방교</t>
+          <t>소방장</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>핵심만 짚어 주어 집중이 잘 됐음</t>
-        </is>
-      </c>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -2561,18 +2545,18 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2585,14 +2569,10 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="R18" t="inlineStr">
-        <is>
-          <t>설명 속도가 빨라 따라가기 어려웠음</t>
-        </is>
-      </c>
+      <c r="R18" t="inlineStr"/>
       <c r="S18" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
@@ -2622,12 +2602,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2635,21 +2615,17 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>쉬는 시간이 짧아 이동하기 바빴음</t>
-        </is>
-      </c>
+      <c r="AB18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026/10/30 오후 04:48:00</t>
+          <t>2026/10/28 오후 04:48:00</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>□□소방서</t>
+          <t>○○소방서</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2659,17 +2635,17 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -2680,12 +2656,12 @@
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -2698,11 +2674,7 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>자료 글씨가 작아 화면이 잘 안 보였음</t>
-        </is>
-      </c>
+      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr">
         <is>
           <t>만족</t>
@@ -2720,7 +2692,7 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="R19" t="inlineStr"/>
@@ -2741,7 +2713,7 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="W19" t="inlineStr"/>
@@ -2752,7 +2724,7 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
@@ -2770,27 +2742,27 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026/10/30 오후 04:51:00</t>
+          <t>2026/10/28 오후 04:51:00</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>□□소방서</t>
+          <t>○○소방서</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>소방사</t>
+          <t>소방교</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -2803,7 +2775,11 @@
           <t>매우 만족</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr"/>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>이론 비중이 높아 실무 내용이 더 필요함</t>
+        </is>
+      </c>
       <c r="I20" t="inlineStr">
         <is>
           <t>매우 만족</t>
@@ -2811,33 +2787,33 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr">
         <is>
-          <t>불만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
@@ -2848,17 +2824,17 @@
       <c r="R20" t="inlineStr"/>
       <c r="S20" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
@@ -2873,7 +2849,7 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
@@ -2883,20 +2859,20 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
-      <c r="AA20" t="inlineStr"/>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>강의실 의자가 불편했음</t>
-        </is>
-      </c>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026/10/30 오후 04:54:00</t>
+          <t>2026/10/28 오후 04:54:00</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2921,23 +2897,23 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -2947,31 +2923,39 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr"/>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>실습 순서를 단계별로 알려 주어 따라가기 쉬웠음</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>만족</t>
-        </is>
-      </c>
-      <c r="R21" t="inlineStr"/>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>이론 비중이 높아 실무 내용이 더 필요함</t>
+        </is>
+      </c>
       <c r="S21" t="inlineStr">
         <is>
           <t>매우 만족</t>
@@ -2984,12 +2968,12 @@
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
@@ -2999,7 +2983,7 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
@@ -3009,7 +2993,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3017,56 +3001,48 @@
           <t>매우 만족</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>교육 운영 안내가 미리 와서 준비하기 좋았음</t>
-        </is>
-      </c>
+      <c r="AB21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026/10/30 오후 04:57:00</t>
+          <t>2026/10/28 오후 04:57:00</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>□□소방서</t>
+          <t>△△소방서</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>소방사</t>
+          <t>소방교</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>교구가 부족해 기다리는 시간이 길었음</t>
-        </is>
-      </c>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -3076,18 +3052,22 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr"/>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>강사님이 열정적으로 진행해 주셨음</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
@@ -3102,14 +3082,10 @@
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>보통</t>
-        </is>
-      </c>
-      <c r="R22" t="inlineStr">
-        <is>
-          <t>강의실이 더워서 집중하기 어려웠음</t>
-        </is>
-      </c>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr"/>
       <c r="S22" t="inlineStr">
         <is>
           <t>만족</t>
@@ -3117,27 +3093,27 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
@@ -3147,7 +3123,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3160,27 +3136,27 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026/10/30 오후 05:00:00</t>
+          <t>2026/10/28 오후 05:00:00</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>□□소방서</t>
+          <t>소방본부</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>소방위</t>
+          <t>소방사</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -3190,22 +3166,18 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>실습 장비가 충분해서 직접 해 볼 수 있었음</t>
-        </is>
-      </c>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -3218,20 +3190,24 @@
           <t>매우 만족</t>
         </is>
       </c>
-      <c r="M23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>핵심만 짚어 주어 집중이 잘 됐음</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>불만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
@@ -3239,7 +3215,11 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="R23" t="inlineStr"/>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>자료가 깔끔하게 정리되어 복습하기 좋았음</t>
+        </is>
+      </c>
       <c r="S23" t="inlineStr">
         <is>
           <t>매우 만족</t>
@@ -3247,17 +3227,17 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
@@ -3290,7 +3270,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026/10/30 오후 05:03:00</t>
+          <t>2026/10/28 오후 05:03:00</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3305,7 +3285,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -3326,7 +3306,7 @@
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3336,23 +3316,23 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3362,13 +3342,17 @@
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>보통</t>
-        </is>
-      </c>
-      <c r="R24" t="inlineStr"/>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>마이크 소리가 작아 뒷자리에서 잘 안 들렸음</t>
+        </is>
+      </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
@@ -3378,12 +3362,12 @@
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="W24" t="inlineStr">
@@ -3391,28 +3375,32 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr"/>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
       <c r="Y24" t="inlineStr">
         <is>
           <t>만족</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
+      <c r="Z24" t="inlineStr"/>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr"/>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>강의실 의자가 불편했음</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026/10/30 오후 05:06:00</t>
+          <t>2026/10/28 오후 05:06:00</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3432,7 +3420,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -3442,10 +3430,14 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr"/>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>자료 글씨가 작아 화면이 잘 안 보였음</t>
+        </is>
+      </c>
       <c r="I25" t="inlineStr">
         <is>
           <t>만족</t>
@@ -3453,22 +3445,22 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>강사님이 열정적으로 진행해 주셨음</t>
+          <t>실습 시간이 부족했음</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -3483,12 +3475,12 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="R25" t="inlineStr"/>
@@ -3499,17 +3491,17 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="W25" t="inlineStr">
@@ -3519,35 +3511,35 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr"/>
       <c r="AA25" t="inlineStr">
         <is>
           <t>매우 만족</t>
         </is>
       </c>
-      <c r="AB25" t="inlineStr"/>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>식당 대기 시간이 길었음</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026/10/30 오후 05:09:00</t>
+          <t>2026/10/28 오후 05:09:00</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>소방본부</t>
+          <t>△△소방서</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -3557,7 +3549,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -3572,7 +3564,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="H26" t="inlineStr"/>
@@ -3583,12 +3575,12 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -3596,34 +3588,30 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>실습 순서를 단계별로 알려 주어 따라가기 쉬웠음</t>
-        </is>
-      </c>
+      <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>이론 비중이 높아 실무 내용이 더 필요함</t>
+          <t>마이크 소리가 작아 뒷자리에서 잘 안 들렸음</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -3633,7 +3621,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -3643,7 +3631,7 @@
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="W26" t="inlineStr">
@@ -3653,17 +3641,17 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3671,11 +3659,7 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>과정 전체 일정 구성이 알찼음</t>
-        </is>
-      </c>
+      <c r="AB26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/samples/survey_rescue13.xlsx
+++ b/samples/survey_rescue13.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB26"/>
+  <dimension ref="A1:AC26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -422,6 +422,33 @@
           <t>구조역량 강화과정 13기 설문 결과(모의)</t>
         </is>
       </c>
+      <c r="B1" t="inlineStr"/>
+      <c r="C1" t="inlineStr"/>
+      <c r="D1" t="inlineStr"/>
+      <c r="E1" t="inlineStr"/>
+      <c r="F1" t="inlineStr"/>
+      <c r="G1" t="inlineStr"/>
+      <c r="H1" t="inlineStr"/>
+      <c r="I1" t="inlineStr"/>
+      <c r="J1" t="inlineStr"/>
+      <c r="K1" t="inlineStr"/>
+      <c r="L1" t="inlineStr"/>
+      <c r="M1" t="inlineStr"/>
+      <c r="N1" t="inlineStr"/>
+      <c r="O1" t="inlineStr"/>
+      <c r="P1" t="inlineStr"/>
+      <c r="Q1" t="inlineStr"/>
+      <c r="R1" t="inlineStr"/>
+      <c r="S1" t="inlineStr"/>
+      <c r="T1" t="inlineStr"/>
+      <c r="U1" t="inlineStr"/>
+      <c r="V1" t="inlineStr"/>
+      <c r="W1" t="inlineStr"/>
+      <c r="X1" t="inlineStr"/>
+      <c r="Y1" t="inlineStr"/>
+      <c r="Z1" t="inlineStr"/>
+      <c r="AA1" t="inlineStr"/>
+      <c r="AB1" t="inlineStr"/>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -431,135 +458,140 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>소속 기관</t>
+          <t>소속</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>현재 계급</t>
+          <t>근무기간</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t>보직</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>구조장비 운용 | 박솔빈 강사 | 태도: 교수님은 성실한 자세로 노력하며 강의(훈련)하였나요?</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>구조장비 운용 | 박솔빈 강사 | 준비성: 훈련환경은 적절하고 장비는 충분했나요?</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>구조장비 운용 | 박솔빈 강사 | 전문성: 교수님은 전문적이고 숙달된 자세로 훈련을 지도했나요?</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>구조장비 운용 | 박솔빈 강사 | 적용성: 재난현장 및 실무에서 활용할 수 있는 훈련인가요?</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>구조장비 운용 | 박솔빈 강사 | 의견: 이 교과목 또는 강사에 대한 의견을 자유롭게 적어 주세요(선택)</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>붕괴사고 대응 | 김새봄 강사 | 태도: 강사는 성실하고 열의 있는 자세로 강의하였습니까?</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>붕괴사고 대응 | 김새봄 강사 | 목표: 강의 내용은 교과목의 학습목표에 맞게 구성되었습니까?</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>붕괴사고 대응 | 김새봄 강사 | 전달: 강사는 강의 내용을 이해하기 쉽게 전달하였습니까?</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>붕괴사고 대응 | 김새봄 강사 | 효과: 강의 내용은 현장 직무 수행에 도움이 되겠습니까?</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>붕괴사고 대응 | 김새봄 강사 | 의견: 이 교과목 또는 강사에 대한 의견을 자유롭게 적어 주세요(선택)</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>수난구조 이론 | 김새봄 강사 | 태도: 강사는 성실하고 열의 있는 자세로 강의하였습니까?</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>수난구조 이론 | 김새봄 강사 | 목표: 강의 내용은 교과목의 학습목표에 맞게 구성되었습니까?</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>수난구조 이론 | 김새봄 강사 | 전달: 강사는 강의 내용을 이해하기 쉽게 전달하였습니까?</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>수난구조 이론 | 김새봄 강사 | 효과: 강의 내용은 현장 직무 수행에 도움이 되겠습니까?</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>수난구조 이론 | 김새봄 강사 | 의견: 이 교과목 또는 강사에 대한 의견을 자유롭게 적어 주세요(선택)</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>공통 | 교육시설환경 | 교재의 품질</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>공통 | 교육시설환경 | 강의실 및 교육기자재</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>공통 | 교육시설환경 | 편의시설</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>공통 | 교육시설환경 | 교직원의 친절도</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>공통 | 구내식당 | 구내식당 이용</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>공통 | 구내식당 | 음식의 간</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>공통 | 구내식당 | 메뉴의 다양성</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AA2" t="inlineStr">
         <is>
           <t>공통 | 구내식당 | 청결도</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>공통 | 구내식당 | 친절도</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>공통 | 과정 운영 | 의견: 이번 과정 운영(일정·시설·안내 등)에 대한 의견을 자유롭게 적어 주세요(선택)</t>
         </is>
@@ -573,27 +605,27 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>□□소방서</t>
+          <t>소방서</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>소방장</t>
+          <t>10년 이상~20년 미만</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>구조</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -603,17 +635,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
           <t>점심 직후 시간이라 집중이 어려웠음, 시간 조정 필요</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -626,12 +658,12 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr">
         <is>
           <t>매우 만족</t>
@@ -644,19 +676,19 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
           <t>사례가 조금 더 있으면 좋겠음</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
       <c r="T3" t="inlineStr">
         <is>
           <t>만족</t>
@@ -694,10 +726,15 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr"/>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -707,27 +744,27 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>□□소방서</t>
+          <t>소방서</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>소방장</t>
+          <t>10년 이상~20년 미만</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>구조</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -735,12 +772,12 @@
           <t>매우 만족</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
           <t>만족</t>
@@ -748,7 +785,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -756,12 +793,12 @@
           <t>보통</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr">
         <is>
           <t>매우 만족</t>
@@ -777,12 +814,12 @@
           <t>매우 만족</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr"/>
       <c r="T4" t="inlineStr">
         <is>
           <t>매우 만족</t>
@@ -795,12 +832,12 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -808,14 +845,19 @@
           <t>매우 만족</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr"/>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>보통</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr"/>
-      <c r="AB4" t="inlineStr">
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr"/>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr"/>
+      <c r="AC4" t="inlineStr">
         <is>
           <t>주차 공간이 부족했음</t>
         </is>
@@ -829,17 +871,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>△△소방서</t>
+          <t>소방서</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>소방사</t>
+          <t>5년 미만</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>구조</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -854,15 +896,15 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
           <t>매우 만족</t>
@@ -878,12 +920,12 @@
           <t>매우 만족</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr">
         <is>
           <t>만족</t>
@@ -891,20 +933,20 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>만족</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr"/>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr"/>
       <c r="T5" t="inlineStr">
         <is>
           <t>만족</t>
@@ -922,7 +964,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -932,20 +974,25 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr"/>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -960,17 +1007,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>소방장</t>
+          <t>10년 이상~20년 미만</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>구조</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -980,23 +1027,23 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>보통</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1004,15 +1051,15 @@
           <t>매우 만족</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1025,20 +1072,20 @@
           <t>매우 만족</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr"/>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>보통</t>
-        </is>
-      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr"/>
       <c r="T6" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1058,12 +1105,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1071,7 +1118,12 @@
           <t>매우 만족</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr"/>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1086,39 +1138,39 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>소방사</t>
+          <t>5년 미만</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>구조</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
           <t>실습 순서를 단계별로 알려 주어 따라가기 쉬웠음</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
       <c r="J7" t="inlineStr">
         <is>
           <t>만족</t>
@@ -1131,59 +1183,59 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>만족</t>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr"/>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr"/>
       <c r="T7" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1193,7 +1245,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1201,7 +1253,12 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr"/>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1216,12 +1273,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>소방위</t>
+          <t>20년 이상</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>구조</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1231,7 +1288,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1239,33 +1296,33 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr">
         <is>
           <t>만족</t>
@@ -1283,14 +1340,14 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
           <t>핵심만 짚어 주어 집중이 잘 됐음</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
       <c r="T8" t="inlineStr">
         <is>
           <t>만족</t>
@@ -1298,7 +1355,7 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1308,7 +1365,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -1323,15 +1380,20 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>만족</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr"/>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1341,17 +1403,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>○○소방서</t>
+          <t>소방서</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>소방위</t>
+          <t>20년 이상</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>구조</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1369,15 +1431,15 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1392,22 +1454,22 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
           <t>실습 시간이 부족했음</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
@@ -1415,12 +1477,12 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr"/>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr"/>
       <c r="T9" t="inlineStr">
         <is>
           <t>매우 만족</t>
@@ -1428,22 +1490,22 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -1453,15 +1515,20 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>만족</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr"/>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1471,22 +1538,22 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>□□소방서</t>
+          <t>소방서</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>소방위</t>
+          <t>20년 이상</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>화재진압</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1499,20 +1566,20 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1520,12 +1587,12 @@
           <t>매우 만족</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr">
         <is>
           <t>만족</t>
@@ -1538,48 +1605,48 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr"/>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr"/>
       <c r="T10" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1587,7 +1654,12 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr"/>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1602,12 +1674,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>소방장</t>
+          <t>10년 이상~20년 미만</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>구조</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1617,7 +1689,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1627,14 +1699,14 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
           <t>질문에 성실하게 답변해 주셔서 좋았음</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
       <c r="J11" t="inlineStr">
         <is>
           <t>만족</t>
@@ -1642,20 +1714,20 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>만족</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr">
         <is>
           <t>만족</t>
@@ -1663,24 +1735,24 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
           <t>교구가 부족해 기다리는 시간이 길었음</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
       <c r="T11" t="inlineStr">
         <is>
           <t>매우 만족</t>
@@ -1688,12 +1760,12 @@
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
@@ -1708,20 +1780,25 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>만족</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr"/>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1731,27 +1808,27 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>□□소방서</t>
+          <t>소방서</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>소방장</t>
+          <t>10년 이상~20년 미만</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>구조</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1759,41 +1836,41 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
@@ -1801,12 +1878,12 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr"/>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr"/>
       <c r="T12" t="inlineStr">
         <is>
           <t>매우 만족</t>
@@ -1814,7 +1891,7 @@
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
@@ -1824,7 +1901,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -1834,12 +1911,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1847,7 +1924,12 @@
           <t>매우 만족</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr"/>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1857,22 +1939,22 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>□□소방서</t>
+          <t>소방서</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>소방위</t>
+          <t>20년 이상</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>구조</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1882,15 +1964,15 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
           <t>만족</t>
@@ -1906,20 +1988,20 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
@@ -1927,15 +2009,15 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="R13" t="inlineStr"/>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr"/>
       <c r="T13" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1945,35 +2027,40 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>만족</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr"/>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1983,43 +2070,43 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>△△소방서</t>
+          <t>소방서</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>소방사</t>
+          <t>5년 미만</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>기타</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>보통</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -2034,14 +2121,14 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
           <t>실습 시간이 부족했음</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
       <c r="O14" t="inlineStr">
         <is>
           <t>만족</t>
@@ -2049,43 +2136,43 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>보통</t>
-        </is>
-      </c>
-      <c r="R14" t="inlineStr"/>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr"/>
       <c r="T14" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
@@ -2093,13 +2180,18 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr"/>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr"/>
       <c r="AB14" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
         <is>
           <t>강의실이 더워서 집중하기 어려웠음</t>
         </is>
@@ -2118,12 +2210,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>소방교</t>
+          <t>5년 이상~10년 미만</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>구조</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -2133,7 +2225,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -2143,14 +2235,14 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
           <t>실습 순서를 단계별로 알려 주어 따라가기 쉬웠음</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
       <c r="J15" t="inlineStr">
         <is>
           <t>만족</t>
@@ -2166,15 +2258,15 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>보통</t>
-        </is>
-      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2184,19 +2276,19 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
           <t>설명 속도가 빨라 따라가기 어려웠음</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
       <c r="T15" t="inlineStr">
         <is>
           <t>만족</t>
@@ -2204,17 +2296,17 @@
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -2229,11 +2321,16 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
-      <c r="AA15" t="inlineStr"/>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
       <c r="AB15" t="inlineStr"/>
+      <c r="AC15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2243,17 +2340,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>○○소방서</t>
+          <t>소방서</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>소방장</t>
+          <t>10년 이상~20년 미만</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>구조</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -2268,15 +2365,15 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
           <t>만족</t>
@@ -2289,27 +2386,27 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
           <t>점심 직후 시간이라 집중이 어려웠음, 시간 조정 필요</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
@@ -2319,22 +2416,22 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
           <t>마이크 소리가 작아 뒷자리에서 잘 안 들렸음</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
@@ -2352,18 +2449,23 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="Y16" t="inlineStr"/>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr"/>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr"/>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2378,17 +2480,17 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>소방장</t>
+          <t>10년 이상~20년 미만</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>구조</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -2401,20 +2503,20 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -2422,12 +2524,12 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr">
         <is>
           <t>만족</t>
@@ -2435,33 +2537,33 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>보통</t>
-        </is>
-      </c>
-      <c r="R17" t="inlineStr"/>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr"/>
       <c r="T17" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
@@ -2471,17 +2573,17 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2489,7 +2591,12 @@
           <t>매우 만족</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr"/>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2504,12 +2611,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>소방장</t>
+          <t>10년 이상~20년 미만</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>행정</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -2524,15 +2631,15 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>보통</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
           <t>만족</t>
@@ -2545,15 +2652,15 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr">
         <is>
           <t>매우 만족</t>
@@ -2561,7 +2668,7 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
@@ -2569,25 +2676,25 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="R18" t="inlineStr"/>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr"/>
       <c r="T18" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
@@ -2602,7 +2709,7 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
@@ -2612,10 +2719,15 @@
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>만족</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr"/>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2625,17 +2737,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>○○소방서</t>
+          <t>소방서</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>소방위</t>
+          <t>20년 이상</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>구조</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -2653,15 +2765,15 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -2674,20 +2786,20 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
@@ -2695,15 +2807,15 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="R19" t="inlineStr"/>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>보통</t>
-        </is>
-      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr"/>
       <c r="T19" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2713,15 +2825,15 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>만족</t>
-        </is>
-      </c>
-      <c r="W19" t="inlineStr"/>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr"/>
       <c r="Y19" t="inlineStr">
         <is>
           <t>매우 만족</t>
@@ -2734,10 +2846,15 @@
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>만족</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr"/>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2747,17 +2864,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>○○소방서</t>
+          <t>소방서</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>소방교</t>
+          <t>5년 이상~10년 미만</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>구조</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -2772,27 +2889,27 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
           <t>이론 비중이 높아 실무 내용이 더 필요함</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -2800,33 +2917,33 @@
           <t>매우 만족</t>
         </is>
       </c>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>만족</t>
-        </is>
-      </c>
-      <c r="R20" t="inlineStr"/>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr"/>
       <c r="T20" t="inlineStr">
         <is>
           <t>매우 만족</t>
@@ -2844,7 +2961,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -2867,7 +2984,12 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr"/>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2882,22 +3004,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>소방위</t>
+          <t>20년 이상</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>구조</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -2905,12 +3027,12 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
           <t>만족</t>
@@ -2928,14 +3050,14 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
           <t>실습 순서를 단계별로 알려 주어 따라가기 쉬웠음</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
       <c r="O21" t="inlineStr">
         <is>
           <t>만족</t>
@@ -2948,19 +3070,19 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
           <t>이론 비중이 높아 실무 내용이 더 필요함</t>
         </is>
       </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
       <c r="T21" t="inlineStr">
         <is>
           <t>매우 만족</t>
@@ -2973,7 +3095,7 @@
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
@@ -2993,7 +3115,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3001,7 +3123,12 @@
           <t>매우 만족</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr"/>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -3011,68 +3138,68 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>△△소방서</t>
+          <t>소방서</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>소방교</t>
+          <t>5년 이상~10년 미만</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>상황·통신</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>만족</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
           <t>강사님이 열정적으로 진행해 주셨음</t>
         </is>
       </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3085,12 +3212,12 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="R22" t="inlineStr"/>
-      <c r="S22" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr"/>
       <c r="T22" t="inlineStr">
         <is>
           <t>만족</t>
@@ -3108,17 +3235,17 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
@@ -3131,7 +3258,12 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="AB22" t="inlineStr"/>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -3146,35 +3278,35 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>소방사</t>
+          <t>5년 미만</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>구조</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>보통</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr">
         <is>
           <t>매우 만족</t>
@@ -3182,24 +3314,24 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
           <t>핵심만 짚어 주어 집중이 잘 됐음</t>
         </is>
       </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
       <c r="O23" t="inlineStr">
         <is>
           <t>만족</t>
@@ -3217,14 +3349,14 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
           <t>자료가 깔끔하게 정리되어 복습하기 좋았음</t>
         </is>
       </c>
-      <c r="S23" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
       <c r="T23" t="inlineStr">
         <is>
           <t>매우 만족</t>
@@ -3232,7 +3364,7 @@
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
@@ -3265,7 +3397,12 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="AB23" t="inlineStr"/>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -3275,17 +3412,17 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>○○소방서</t>
+          <t>소방서</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>소방교</t>
+          <t>5년 이상~10년 미만</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>구조</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -3295,7 +3432,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -3303,15 +3440,15 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -3324,12 +3461,12 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="O24" t="inlineStr">
         <is>
           <t>매우 만족</t>
@@ -3342,19 +3479,19 @@
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
           <t>마이크 소리가 작아 뒷자리에서 잘 안 들렸음</t>
         </is>
       </c>
-      <c r="S24" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
       <c r="T24" t="inlineStr">
         <is>
           <t>매우 만족</t>
@@ -3362,7 +3499,7 @@
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
@@ -3385,13 +3522,18 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr"/>
-      <c r="AA24" t="inlineStr">
-        <is>
-          <t>보통</t>
-        </is>
-      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr"/>
       <c r="AB24" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
         <is>
           <t>강의실 의자가 불편했음</t>
         </is>
@@ -3405,17 +3547,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>○○소방서</t>
+          <t>소방서</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>소방장</t>
+          <t>10년 이상~20년 미만</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>구조</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -3425,24 +3567,24 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
           <t>자료 글씨가 작아 화면이 잘 안 보였음</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
       <c r="J25" t="inlineStr">
         <is>
           <t>만족</t>
@@ -3455,27 +3597,27 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
           <t>실습 시간이 부족했음</t>
         </is>
       </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
@@ -3483,12 +3625,12 @@
           <t>매우 만족</t>
         </is>
       </c>
-      <c r="R25" t="inlineStr"/>
-      <c r="S25" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr"/>
       <c r="T25" t="inlineStr">
         <is>
           <t>만족</t>
@@ -3501,31 +3643,36 @@
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>만족</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr"/>
-      <c r="AA25" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr"/>
       <c r="AB25" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
         <is>
           <t>식당 대기 시간이 길었음</t>
         </is>
@@ -3539,17 +3686,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>△△소방서</t>
+          <t>소방서</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>소방위</t>
+          <t>20년 이상</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>예방·안전</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -3564,18 +3711,18 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -3588,37 +3735,37 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="M26" t="inlineStr"/>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="O26" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
           <t>마이크 소리가 작아 뒷자리에서 잘 안 들렸음</t>
         </is>
       </c>
-      <c r="S26" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
       <c r="T26" t="inlineStr">
         <is>
           <t>만족</t>
@@ -3626,7 +3773,7 @@
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
@@ -3641,12 +3788,12 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
@@ -3656,10 +3803,15 @@
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>만족</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr"/>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
